--- a/gauntlet_data.global.xlsx
+++ b/gauntlet_data.global.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\hzz\work\MutualExclusionAllocator\repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F151A73F-4BF4-4A6C-B3C2-AC2E3F201173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEA0DFA-E564-4F3B-81DF-461EBECD9906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1084,7 +1084,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="4">
-        <v>18.100000000000001</v>
+        <v>18</v>
       </c>
       <c r="D2" s="4">
         <v>18.5</v>
@@ -1120,7 +1120,9 @@
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="T2" s="4">
+        <v>18.8</v>
+      </c>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
@@ -1131,7 +1133,7 @@
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4">
-        <v>18.89</v>
+        <v>18.8</v>
       </c>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4">
@@ -1473,7 +1475,9 @@
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="4">
+        <v>22.4</v>
+      </c>
       <c r="D6" s="4">
         <v>22.5</v>
       </c>
@@ -1814,7 +1818,9 @@
         <v>27.75</v>
       </c>
       <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
+      <c r="U9" s="4">
+        <v>30.419</v>
+      </c>
       <c r="V9" s="4"/>
       <c r="W9" s="4">
         <v>27.3</v>
@@ -2069,7 +2075,9 @@
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="4">
+        <v>21.7</v>
+      </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4">
@@ -2587,7 +2595,7 @@
         <v>19.559999999999999</v>
       </c>
       <c r="D18" s="4">
-        <v>19.600000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="E18" s="4">
         <v>19.170000000000002</v>
@@ -2598,7 +2606,9 @@
       <c r="G18" s="4">
         <v>19.89</v>
       </c>
-      <c r="H18" s="4"/>
+      <c r="H18" s="4">
+        <v>19.45</v>
+      </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -2614,7 +2624,9 @@
       </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
+      <c r="T18" s="4">
+        <v>19.9</v>
+      </c>
       <c r="U18" s="4">
         <v>20.21</v>
       </c>
@@ -3730,7 +3742,7 @@
       </c>
       <c r="J30" s="4"/>
       <c r="K30" s="4">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -5062,6 +5074,21 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A32:A33"/>
@@ -5069,21 +5096,6 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8124,6 +8136,21 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A32:A33"/>
@@ -8131,21 +8158,6 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8824,6 +8836,21 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A32:A33"/>
@@ -8831,21 +8858,6 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9222,6 +9234,21 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A32:A33"/>
@@ -9229,21 +9256,6 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9956,6 +9968,21 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A32:A33"/>
@@ -9963,21 +9990,6 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10656,6 +10668,21 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A32:A33"/>
@@ -10663,21 +10690,6 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11356,6 +11368,21 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A32:A33"/>
@@ -11363,21 +11390,6 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11754,6 +11766,21 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A32:A33"/>
@@ -11761,21 +11788,6 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11784,7 +11796,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -11797,6 +11809,11 @@
     <col min="14" max="14" width="10" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
     <col min="16" max="18" width="10" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="26" customHeight="1">
@@ -11853,6 +11870,31 @@
       </c>
       <c r="R1" s="1" t="s">
         <v>145</v>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>21c</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>超光孙</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>divo</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>杰孙</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>恶魔</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:18" ht="22" customHeight="1">
@@ -11884,6 +11926,11 @@
       <c r="R2" s="4">
         <v>18.899999999999999</v>
       </c>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
     </row>
     <row r="3" spans="1:18" ht="22" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -11924,6 +11971,11 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
     </row>
     <row r="4" spans="1:18" ht="22" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -11972,6 +12024,17 @@
         <v>22.82</v>
       </c>
       <c r="R4" s="4"/>
+      <c r="S4" s="4">
+        <v>22</v>
+      </c>
+      <c r="T4" s="4">
+        <v>21.6</v>
+      </c>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4">
+        <v>21.7</v>
+      </c>
+      <c r="W4" s="4"/>
     </row>
     <row r="5" spans="1:18" ht="22" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -12010,6 +12073,15 @@
       </c>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
+      <c r="S5" s="4">
+        <v>17.6</v>
+      </c>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4">
+        <v>18.399</v>
+      </c>
     </row>
     <row r="6" spans="1:18" ht="22" customHeight="1">
       <c r="A6" s="2" t="s">
@@ -12030,7 +12102,7 @@
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4">
-        <v>18.75</v>
+        <v>18.7</v>
       </c>
       <c r="I6" s="4">
         <v>17.87</v>
@@ -12044,6 +12116,13 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4">
+        <v>18.5</v>
+      </c>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
     </row>
     <row r="7" spans="1:18" ht="22" customHeight="1">
       <c r="A7" s="2" t="s">
@@ -12072,6 +12151,11 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
     </row>
     <row r="8" spans="1:18" ht="22" customHeight="1">
       <c r="A8" s="2" t="s">
@@ -12100,6 +12184,11 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
     </row>
     <row r="9" spans="1:18" ht="22" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -12136,6 +12225,11 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
@@ -12166,6 +12260,11 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/gauntlet_data.global.xlsx
+++ b/gauntlet_data.global.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\hzz\work\MutualExclusionAllocator\repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E37C897-7F8B-4087-B943-963C98EAFECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F43A4E-F073-4CC0-AF28-1EE38F085B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="163">
   <si>
     <t>大地图</t>
   </si>
@@ -515,6 +515,14 @@
   </si>
   <si>
     <t>✓</t>
+  </si>
+  <si>
+    <t>dose</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>evozr1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -646,7 +654,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -662,6 +670,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -879,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BG45"/>
+  <dimension ref="A1:BI45"/>
   <sheetFormatPr defaultColWidth="7.453125" defaultRowHeight="14"/>
   <cols>
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="1" max="1" width="14.36328125" bestFit="1" customWidth="1"/>
@@ -933,17 +947,19 @@
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="49" max="49" width="7.453125" customWidth="1"/>
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="50" max="50" width="7.453125" customWidth="1"/>
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="51" max="51" width="7.453125" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="52" max="52" width="12.0" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="52" max="52" width="7.453125" customWidth="1"/>
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="53" max="53" width="7.453125" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="54" max="54" width="12.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="55" max="55" width="10.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="56" max="56" width="7.453125" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="57" max="57" width="7.453125" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="58" max="58" width="9.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="59" max="59" width="10.0" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="54" max="54" width="9.0" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="55" max="55" width="7.453125" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="56" max="56" width="12.0" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="57" max="57" width="10.0" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="58" max="58" width="7.453125" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="59" max="59" width="7.453125" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="60" max="60" width="9.0" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="61" max="61" width="10.0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59">
+    <row r="1" spans="1:61">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1097,33 +1113,41 @@
       <c r="AY1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AZ1" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="BA1" s="3" t="s">
+      <c r="AZ1" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="BA1" s="3" t="inlineStr">
+        <is>
+          <t>urs</t>
+        </is>
+      </c>
+      <c r="BB1" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="BC1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BD1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BE1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BF1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BG1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BH1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BI1" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:59">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:61">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1206,17 +1230,19 @@
       <c r="AW2" s="5"/>
       <c r="AX2" s="5"/>
       <c r="AY2" s="5"/>
-      <c r="AZ2" s="5"/>
+      <c r="AZ2" s="7"/>
       <c r="BA2" s="5"/>
-      <c r="BB2" s="5"/>
+      <c r="BB2" s="7"/>
       <c r="BC2" s="5"/>
       <c r="BD2" s="5"/>
       <c r="BE2" s="5"/>
       <c r="BF2" s="5"/>
       <c r="BG2" s="5"/>
-    </row>
-    <row r="3" spans="1:59">
-      <c r="A3" s="8" t="s">
+      <c r="BH2" s="5"/>
+      <c r="BI2" s="5"/>
+    </row>
+    <row r="3" spans="1:61">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1321,17 +1347,19 @@
       <c r="AW3" s="5"/>
       <c r="AX3" s="5"/>
       <c r="AY3" s="5"/>
-      <c r="AZ3" s="5"/>
+      <c r="AZ3" s="7"/>
       <c r="BA3" s="5"/>
-      <c r="BB3" s="5"/>
+      <c r="BB3" s="7"/>
       <c r="BC3" s="5"/>
       <c r="BD3" s="5"/>
       <c r="BE3" s="5"/>
       <c r="BF3" s="5"/>
       <c r="BG3" s="5"/>
-    </row>
-    <row r="4" spans="1:59">
-      <c r="A4" s="7" t="s">
+      <c r="BH3" s="5"/>
+      <c r="BI3" s="5"/>
+    </row>
+    <row r="4" spans="1:61">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1416,17 +1444,21 @@
       <c r="AW4" s="5"/>
       <c r="AX4" s="5"/>
       <c r="AY4" s="5"/>
-      <c r="AZ4" s="5"/>
+      <c r="AZ4" s="7"/>
       <c r="BA4" s="5"/>
-      <c r="BB4" s="5"/>
+      <c r="BB4" s="7">
+        <v>17.690000000000001</v>
+      </c>
       <c r="BC4" s="5"/>
       <c r="BD4" s="5"/>
       <c r="BE4" s="5"/>
       <c r="BF4" s="5"/>
       <c r="BG4" s="5"/>
-    </row>
-    <row r="5" spans="1:59">
-      <c r="A5" s="8" t="s">
+      <c r="BH4" s="5"/>
+      <c r="BI4" s="5"/>
+    </row>
+    <row r="5" spans="1:61">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1505,17 +1537,19 @@
       <c r="AW5" s="5"/>
       <c r="AX5" s="5"/>
       <c r="AY5" s="5"/>
-      <c r="AZ5" s="5"/>
+      <c r="AZ5" s="7"/>
       <c r="BA5" s="5"/>
-      <c r="BB5" s="5"/>
+      <c r="BB5" s="7"/>
       <c r="BC5" s="5"/>
       <c r="BD5" s="5"/>
       <c r="BE5" s="5"/>
       <c r="BF5" s="5"/>
       <c r="BG5" s="5"/>
-    </row>
-    <row r="6" spans="1:59">
-      <c r="A6" s="7" t="s">
+      <c r="BH5" s="5"/>
+      <c r="BI5" s="5"/>
+    </row>
+    <row r="6" spans="1:61">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -1598,17 +1632,19 @@
       <c r="AW6" s="5"/>
       <c r="AX6" s="5"/>
       <c r="AY6" s="5"/>
-      <c r="AZ6" s="5"/>
+      <c r="AZ6" s="7"/>
       <c r="BA6" s="5"/>
-      <c r="BB6" s="5"/>
+      <c r="BB6" s="7"/>
       <c r="BC6" s="5"/>
       <c r="BD6" s="5"/>
       <c r="BE6" s="5"/>
       <c r="BF6" s="5"/>
       <c r="BG6" s="5"/>
-    </row>
-    <row r="7" spans="1:59">
-      <c r="A7" s="8" t="s">
+      <c r="BH6" s="5"/>
+      <c r="BI6" s="5"/>
+    </row>
+    <row r="7" spans="1:61">
+      <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -1631,10 +1667,10 @@
         <v>20.95</v>
       </c>
       <c r="I7" s="5">
-        <v>21.33</v>
+        <v>21.25</v>
       </c>
       <c r="J7" s="5">
-        <v>20.45</v>
+        <v>20.329999999999998</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5">
@@ -1697,17 +1733,19 @@
       <c r="AW7" s="5"/>
       <c r="AX7" s="5"/>
       <c r="AY7" s="5"/>
-      <c r="AZ7" s="5"/>
+      <c r="AZ7" s="7"/>
       <c r="BA7" s="5"/>
-      <c r="BB7" s="5"/>
+      <c r="BB7" s="7"/>
       <c r="BC7" s="5"/>
       <c r="BD7" s="5"/>
       <c r="BE7" s="5"/>
       <c r="BF7" s="5"/>
       <c r="BG7" s="5"/>
-    </row>
-    <row r="8" spans="1:59">
-      <c r="A8" s="7" t="s">
+      <c r="BH7" s="5"/>
+      <c r="BI7" s="5"/>
+    </row>
+    <row r="8" spans="1:61">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1740,7 +1778,7 @@
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
-        <v>24.7</v>
+        <v>24.35</v>
       </c>
       <c r="N8" s="5">
         <v>24.78</v>
@@ -1798,17 +1836,19 @@
       <c r="AW8" s="5"/>
       <c r="AX8" s="5"/>
       <c r="AY8" s="5"/>
-      <c r="AZ8" s="5"/>
+      <c r="AZ8" s="7"/>
       <c r="BA8" s="5"/>
-      <c r="BB8" s="5"/>
+      <c r="BB8" s="7"/>
       <c r="BC8" s="5"/>
       <c r="BD8" s="5"/>
       <c r="BE8" s="5"/>
       <c r="BF8" s="5"/>
       <c r="BG8" s="5"/>
-    </row>
-    <row r="9" spans="1:59">
-      <c r="A9" s="8" t="s">
+      <c r="BH8" s="5"/>
+      <c r="BI8" s="5"/>
+    </row>
+    <row r="9" spans="1:61">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -1911,17 +1951,19 @@
       <c r="AW9" s="5"/>
       <c r="AX9" s="5"/>
       <c r="AY9" s="5"/>
-      <c r="AZ9" s="5"/>
+      <c r="AZ9" s="7"/>
       <c r="BA9" s="5"/>
-      <c r="BB9" s="5"/>
+      <c r="BB9" s="7"/>
       <c r="BC9" s="5"/>
       <c r="BD9" s="5"/>
       <c r="BE9" s="5"/>
       <c r="BF9" s="5"/>
       <c r="BG9" s="5"/>
-    </row>
-    <row r="10" spans="1:59">
-      <c r="A10" s="7" t="s">
+      <c r="BH9" s="5"/>
+      <c r="BI9" s="5"/>
+    </row>
+    <row r="10" spans="1:61">
+      <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -2000,17 +2042,19 @@
       <c r="AW10" s="5"/>
       <c r="AX10" s="5"/>
       <c r="AY10" s="5"/>
-      <c r="AZ10" s="5"/>
+      <c r="AZ10" s="7"/>
       <c r="BA10" s="5"/>
-      <c r="BB10" s="5"/>
+      <c r="BB10" s="7"/>
       <c r="BC10" s="5"/>
       <c r="BD10" s="5"/>
       <c r="BE10" s="5"/>
       <c r="BF10" s="5"/>
       <c r="BG10" s="5"/>
-    </row>
-    <row r="11" spans="1:59">
-      <c r="A11" s="8" t="s">
+      <c r="BH10" s="5"/>
+      <c r="BI10" s="5"/>
+    </row>
+    <row r="11" spans="1:61">
+      <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -2070,7 +2114,9 @@
       <c r="Z11" s="5">
         <v>22.15</v>
       </c>
-      <c r="AA11" s="5"/>
+      <c r="AA11" s="5">
+        <v>22.45</v>
+      </c>
       <c r="AB11" s="5"/>
       <c r="AC11" s="5"/>
       <c r="AD11" s="5">
@@ -2105,17 +2151,19 @@
       <c r="AW11" s="5"/>
       <c r="AX11" s="5"/>
       <c r="AY11" s="5"/>
-      <c r="AZ11" s="5"/>
+      <c r="AZ11" s="7"/>
       <c r="BA11" s="5"/>
-      <c r="BB11" s="5"/>
+      <c r="BB11" s="7"/>
       <c r="BC11" s="5"/>
       <c r="BD11" s="5"/>
       <c r="BE11" s="5"/>
       <c r="BF11" s="5"/>
       <c r="BG11" s="5"/>
-    </row>
-    <row r="12" spans="1:59">
-      <c r="A12" s="7" t="s">
+      <c r="BH11" s="5"/>
+      <c r="BI11" s="5"/>
+    </row>
+    <row r="12" spans="1:61">
+      <c r="A12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2182,17 +2230,19 @@
       <c r="AW12" s="5"/>
       <c r="AX12" s="5"/>
       <c r="AY12" s="5"/>
-      <c r="AZ12" s="5"/>
+      <c r="AZ12" s="7"/>
       <c r="BA12" s="5"/>
-      <c r="BB12" s="5"/>
+      <c r="BB12" s="7"/>
       <c r="BC12" s="5"/>
       <c r="BD12" s="5"/>
       <c r="BE12" s="5"/>
       <c r="BF12" s="5"/>
       <c r="BG12" s="5"/>
-    </row>
-    <row r="13" spans="1:59">
-      <c r="A13" s="8" t="s">
+      <c r="BH12" s="5"/>
+      <c r="BI12" s="5"/>
+    </row>
+    <row r="13" spans="1:61">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -2269,17 +2319,19 @@
       <c r="AW13" s="5"/>
       <c r="AX13" s="5"/>
       <c r="AY13" s="5"/>
-      <c r="AZ13" s="5"/>
+      <c r="AZ13" s="7"/>
       <c r="BA13" s="5"/>
-      <c r="BB13" s="5"/>
+      <c r="BB13" s="7"/>
       <c r="BC13" s="5"/>
       <c r="BD13" s="5"/>
       <c r="BE13" s="5"/>
       <c r="BF13" s="5"/>
       <c r="BG13" s="5"/>
-    </row>
-    <row r="14" spans="1:59">
-      <c r="A14" s="7" t="s">
+      <c r="BH13" s="5"/>
+      <c r="BI13" s="5"/>
+    </row>
+    <row r="14" spans="1:61">
+      <c r="A14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -2297,7 +2349,9 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+      <c r="I14" s="5">
+        <v>18.32</v>
+      </c>
       <c r="J14" s="5">
         <v>17.47</v>
       </c>
@@ -2346,17 +2400,19 @@
       <c r="AW14" s="5"/>
       <c r="AX14" s="5"/>
       <c r="AY14" s="5"/>
-      <c r="AZ14" s="5"/>
+      <c r="AZ14" s="7"/>
       <c r="BA14" s="5"/>
-      <c r="BB14" s="5"/>
+      <c r="BB14" s="7"/>
       <c r="BC14" s="5"/>
       <c r="BD14" s="5"/>
       <c r="BE14" s="5"/>
       <c r="BF14" s="5"/>
       <c r="BG14" s="5"/>
-    </row>
-    <row r="15" spans="1:59">
-      <c r="A15" s="8" t="s">
+      <c r="BH14" s="5"/>
+      <c r="BI14" s="5"/>
+    </row>
+    <row r="15" spans="1:61">
+      <c r="A15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -2439,17 +2495,19 @@
       <c r="AW15" s="5"/>
       <c r="AX15" s="5"/>
       <c r="AY15" s="5"/>
-      <c r="AZ15" s="5"/>
+      <c r="AZ15" s="7"/>
       <c r="BA15" s="5"/>
-      <c r="BB15" s="5"/>
+      <c r="BB15" s="7"/>
       <c r="BC15" s="5"/>
       <c r="BD15" s="5"/>
       <c r="BE15" s="5"/>
       <c r="BF15" s="5"/>
       <c r="BG15" s="5"/>
-    </row>
-    <row r="16" spans="1:59">
-      <c r="A16" s="7" t="s">
+      <c r="BH15" s="5"/>
+      <c r="BI15" s="5"/>
+    </row>
+    <row r="16" spans="1:61">
+      <c r="A16" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -2540,17 +2598,19 @@
       <c r="AW16" s="5"/>
       <c r="AX16" s="5"/>
       <c r="AY16" s="5"/>
-      <c r="AZ16" s="5"/>
+      <c r="AZ16" s="7"/>
       <c r="BA16" s="5"/>
-      <c r="BB16" s="5"/>
+      <c r="BB16" s="7"/>
       <c r="BC16" s="5"/>
       <c r="BD16" s="5"/>
       <c r="BE16" s="5"/>
       <c r="BF16" s="5"/>
       <c r="BG16" s="5"/>
-    </row>
-    <row r="17" spans="1:59">
-      <c r="A17" s="8" t="s">
+      <c r="BH16" s="5"/>
+      <c r="BI16" s="5"/>
+    </row>
+    <row r="17" spans="1:61">
+      <c r="A17" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -2621,17 +2681,21 @@
       <c r="AW17" s="5"/>
       <c r="AX17" s="5"/>
       <c r="AY17" s="5"/>
-      <c r="AZ17" s="5"/>
+      <c r="AZ17" s="7"/>
       <c r="BA17" s="5"/>
-      <c r="BB17" s="5"/>
+      <c r="BB17" s="7">
+        <v>18.72</v>
+      </c>
       <c r="BC17" s="5"/>
       <c r="BD17" s="5"/>
       <c r="BE17" s="5"/>
       <c r="BF17" s="5"/>
       <c r="BG17" s="5"/>
-    </row>
-    <row r="18" spans="1:59">
-      <c r="A18" s="7" t="s">
+      <c r="BH17" s="5"/>
+      <c r="BI17" s="5"/>
+    </row>
+    <row r="18" spans="1:61">
+      <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -2714,17 +2778,21 @@
       <c r="AW18" s="5"/>
       <c r="AX18" s="5"/>
       <c r="AY18" s="5"/>
-      <c r="AZ18" s="5"/>
+      <c r="AZ18" s="7"/>
       <c r="BA18" s="5"/>
-      <c r="BB18" s="5"/>
+      <c r="BB18" s="7">
+        <v>19.7</v>
+      </c>
       <c r="BC18" s="5"/>
       <c r="BD18" s="5"/>
       <c r="BE18" s="5"/>
       <c r="BF18" s="5"/>
       <c r="BG18" s="5"/>
-    </row>
-    <row r="19" spans="1:59">
-      <c r="A19" s="8" t="s">
+      <c r="BH18" s="5"/>
+      <c r="BI18" s="5"/>
+    </row>
+    <row r="19" spans="1:61">
+      <c r="A19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -2817,17 +2885,19 @@
       <c r="AW19" s="5"/>
       <c r="AX19" s="5"/>
       <c r="AY19" s="5"/>
-      <c r="AZ19" s="5"/>
+      <c r="AZ19" s="7"/>
       <c r="BA19" s="5"/>
-      <c r="BB19" s="5"/>
+      <c r="BB19" s="7"/>
       <c r="BC19" s="5"/>
       <c r="BD19" s="5"/>
       <c r="BE19" s="5"/>
       <c r="BF19" s="5"/>
       <c r="BG19" s="5"/>
-    </row>
-    <row r="20" spans="1:59">
-      <c r="A20" s="7" t="s">
+      <c r="BH19" s="5"/>
+      <c r="BI19" s="5"/>
+    </row>
+    <row r="20" spans="1:61">
+      <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -2859,7 +2929,9 @@
         <v>22.45</v>
       </c>
       <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
+      <c r="M20" s="5">
+        <v>21.88</v>
+      </c>
       <c r="N20" s="5">
         <v>22.45</v>
       </c>
@@ -2871,7 +2943,9 @@
       </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
+      <c r="S20" s="5">
+        <v>22.07</v>
+      </c>
       <c r="T20" s="5"/>
       <c r="U20" s="5">
         <v>23.96</v>
@@ -2906,17 +2980,19 @@
       <c r="AW20" s="5"/>
       <c r="AX20" s="5"/>
       <c r="AY20" s="5"/>
-      <c r="AZ20" s="5"/>
+      <c r="AZ20" s="7"/>
       <c r="BA20" s="5"/>
-      <c r="BB20" s="5"/>
+      <c r="BB20" s="7"/>
       <c r="BC20" s="5"/>
       <c r="BD20" s="5"/>
       <c r="BE20" s="5"/>
       <c r="BF20" s="5"/>
       <c r="BG20" s="5"/>
-    </row>
-    <row r="21" spans="1:59">
-      <c r="A21" s="8" t="s">
+      <c r="BH20" s="5"/>
+      <c r="BI20" s="5"/>
+    </row>
+    <row r="21" spans="1:61">
+      <c r="A21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -3003,17 +3079,21 @@
       <c r="AW21" s="5"/>
       <c r="AX21" s="5"/>
       <c r="AY21" s="5"/>
-      <c r="AZ21" s="5"/>
+      <c r="AZ21" s="7"/>
       <c r="BA21" s="5"/>
-      <c r="BB21" s="5"/>
+      <c r="BB21" s="7">
+        <v>20.49</v>
+      </c>
       <c r="BC21" s="5"/>
       <c r="BD21" s="5"/>
       <c r="BE21" s="5"/>
       <c r="BF21" s="5"/>
       <c r="BG21" s="5"/>
-    </row>
-    <row r="22" spans="1:59">
-      <c r="A22" s="7" t="s">
+      <c r="BH21" s="5"/>
+      <c r="BI21" s="5"/>
+    </row>
+    <row r="22" spans="1:61">
+      <c r="A22" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -3096,17 +3176,19 @@
       <c r="AW22" s="5"/>
       <c r="AX22" s="5"/>
       <c r="AY22" s="5"/>
-      <c r="AZ22" s="5"/>
+      <c r="AZ22" s="7"/>
       <c r="BA22" s="5"/>
-      <c r="BB22" s="5"/>
+      <c r="BB22" s="7"/>
       <c r="BC22" s="5"/>
       <c r="BD22" s="5"/>
       <c r="BE22" s="5"/>
       <c r="BF22" s="5"/>
       <c r="BG22" s="5"/>
-    </row>
-    <row r="23" spans="1:59">
-      <c r="A23" s="8" t="s">
+      <c r="BH22" s="5"/>
+      <c r="BI22" s="5"/>
+    </row>
+    <row r="23" spans="1:61">
+      <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -3181,17 +3263,21 @@
       <c r="AW23" s="5"/>
       <c r="AX23" s="5"/>
       <c r="AY23" s="5"/>
-      <c r="AZ23" s="5"/>
+      <c r="AZ23" s="7"/>
       <c r="BA23" s="5"/>
-      <c r="BB23" s="5"/>
+      <c r="BB23" s="7">
+        <v>21.49</v>
+      </c>
       <c r="BC23" s="5"/>
       <c r="BD23" s="5"/>
       <c r="BE23" s="5"/>
       <c r="BF23" s="5"/>
       <c r="BG23" s="5"/>
-    </row>
-    <row r="24" spans="1:59">
-      <c r="A24" s="7" t="s">
+      <c r="BH23" s="5"/>
+      <c r="BI23" s="5"/>
+    </row>
+    <row r="24" spans="1:61">
+      <c r="A24" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -3207,7 +3293,7 @@
         <v>31.35</v>
       </c>
       <c r="F24" s="5">
-        <v>32.200000000000003</v>
+        <v>31.89</v>
       </c>
       <c r="G24" s="5">
         <v>34.130000000000003</v>
@@ -3280,17 +3366,19 @@
       <c r="AW24" s="5"/>
       <c r="AX24" s="5"/>
       <c r="AY24" s="5"/>
-      <c r="AZ24" s="5"/>
+      <c r="AZ24" s="7"/>
       <c r="BA24" s="5"/>
-      <c r="BB24" s="5"/>
+      <c r="BB24" s="7"/>
       <c r="BC24" s="5"/>
       <c r="BD24" s="5"/>
       <c r="BE24" s="5"/>
       <c r="BF24" s="5"/>
       <c r="BG24" s="5"/>
-    </row>
-    <row r="25" spans="1:59">
-      <c r="A25" s="8" t="s">
+      <c r="BH24" s="5"/>
+      <c r="BI24" s="5"/>
+    </row>
+    <row r="25" spans="1:61">
+      <c r="A25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -3383,17 +3471,19 @@
       <c r="AW25" s="5"/>
       <c r="AX25" s="5"/>
       <c r="AY25" s="5"/>
-      <c r="AZ25" s="5"/>
+      <c r="AZ25" s="7"/>
       <c r="BA25" s="5"/>
-      <c r="BB25" s="5"/>
+      <c r="BB25" s="7"/>
       <c r="BC25" s="5"/>
       <c r="BD25" s="5"/>
       <c r="BE25" s="5"/>
       <c r="BF25" s="5"/>
       <c r="BG25" s="5"/>
-    </row>
-    <row r="26" spans="1:59">
-      <c r="A26" s="7" t="s">
+      <c r="BH25" s="5"/>
+      <c r="BI25" s="5"/>
+    </row>
+    <row r="26" spans="1:61">
+      <c r="A26" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -3414,11 +3504,9 @@
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5">
-        <v>25.89</v>
-      </c>
-      <c r="J26" s="5">
         <v>25.8</v>
       </c>
+      <c r="J26" s="5"/>
       <c r="K26" s="5">
         <v>26.35</v>
       </c>
@@ -3482,17 +3570,21 @@
       <c r="AW26" s="5"/>
       <c r="AX26" s="5"/>
       <c r="AY26" s="5"/>
-      <c r="AZ26" s="5"/>
+      <c r="AZ26" s="7"/>
       <c r="BA26" s="5"/>
-      <c r="BB26" s="5"/>
+      <c r="BB26" s="7">
+        <v>26.53</v>
+      </c>
       <c r="BC26" s="5"/>
       <c r="BD26" s="5"/>
       <c r="BE26" s="5"/>
       <c r="BF26" s="5"/>
       <c r="BG26" s="5"/>
-    </row>
-    <row r="27" spans="1:59">
-      <c r="A27" s="8" t="s">
+      <c r="BH26" s="5"/>
+      <c r="BI26" s="5"/>
+    </row>
+    <row r="27" spans="1:61">
+      <c r="A27" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -3573,17 +3665,19 @@
       <c r="AW27" s="5"/>
       <c r="AX27" s="5"/>
       <c r="AY27" s="5"/>
-      <c r="AZ27" s="5"/>
+      <c r="AZ27" s="7"/>
       <c r="BA27" s="5"/>
-      <c r="BB27" s="5"/>
+      <c r="BB27" s="7"/>
       <c r="BC27" s="5"/>
       <c r="BD27" s="5"/>
       <c r="BE27" s="5"/>
       <c r="BF27" s="5"/>
       <c r="BG27" s="5"/>
-    </row>
-    <row r="28" spans="1:59">
-      <c r="A28" s="7" t="s">
+      <c r="BH27" s="5"/>
+      <c r="BI27" s="5"/>
+    </row>
+    <row r="28" spans="1:61">
+      <c r="A28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -3599,10 +3693,10 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
-        <v>30.85</v>
+        <v>30.7</v>
       </c>
       <c r="I28" s="5">
-        <v>31.53</v>
+        <v>31.45</v>
       </c>
       <c r="J28" s="5">
         <v>31.95</v>
@@ -3660,17 +3754,19 @@
       <c r="AW28" s="5"/>
       <c r="AX28" s="5"/>
       <c r="AY28" s="5"/>
-      <c r="AZ28" s="5"/>
+      <c r="AZ28" s="7"/>
       <c r="BA28" s="5"/>
-      <c r="BB28" s="5"/>
+      <c r="BB28" s="7"/>
       <c r="BC28" s="5"/>
       <c r="BD28" s="5"/>
       <c r="BE28" s="5"/>
       <c r="BF28" s="5"/>
       <c r="BG28" s="5"/>
-    </row>
-    <row r="29" spans="1:59">
-      <c r="A29" s="8" t="s">
+      <c r="BH28" s="5"/>
+      <c r="BI28" s="5"/>
+    </row>
+    <row r="29" spans="1:61">
+      <c r="A29" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -3680,10 +3776,10 @@
         <v>30.25</v>
       </c>
       <c r="D29" s="5">
-        <v>32.53</v>
+        <v>32.07</v>
       </c>
       <c r="E29" s="5">
-        <v>32.630000000000003</v>
+        <v>32.39</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5">
@@ -3757,17 +3853,19 @@
       <c r="AW29" s="5"/>
       <c r="AX29" s="5"/>
       <c r="AY29" s="5"/>
-      <c r="AZ29" s="5"/>
+      <c r="AZ29" s="7"/>
       <c r="BA29" s="5"/>
-      <c r="BB29" s="5"/>
+      <c r="BB29" s="7"/>
       <c r="BC29" s="5"/>
       <c r="BD29" s="5"/>
       <c r="BE29" s="5"/>
       <c r="BF29" s="5"/>
       <c r="BG29" s="5"/>
-    </row>
-    <row r="30" spans="1:59">
-      <c r="A30" s="7" t="s">
+      <c r="BH29" s="5"/>
+      <c r="BI29" s="5"/>
+    </row>
+    <row r="30" spans="1:61">
+      <c r="A30" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -3832,19 +3930,21 @@
       <c r="AW30" s="5"/>
       <c r="AX30" s="5"/>
       <c r="AY30" s="5"/>
-      <c r="AZ30" s="5">
+      <c r="AZ30" s="7"/>
+      <c r="BA30" s="5">
         <v>26.16</v>
       </c>
-      <c r="BA30" s="5"/>
-      <c r="BB30" s="5"/>
+      <c r="BB30" s="7"/>
       <c r="BC30" s="5"/>
       <c r="BD30" s="5"/>
       <c r="BE30" s="5"/>
       <c r="BF30" s="5"/>
       <c r="BG30" s="5"/>
-    </row>
-    <row r="31" spans="1:59">
-      <c r="A31" s="8" t="s">
+      <c r="BH30" s="5"/>
+      <c r="BI30" s="5"/>
+    </row>
+    <row r="31" spans="1:61">
+      <c r="A31" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -3937,17 +4037,19 @@
       <c r="AW31" s="5"/>
       <c r="AX31" s="5"/>
       <c r="AY31" s="5"/>
-      <c r="AZ31" s="5"/>
+      <c r="AZ31" s="7"/>
       <c r="BA31" s="5"/>
-      <c r="BB31" s="5"/>
+      <c r="BB31" s="7"/>
       <c r="BC31" s="5"/>
       <c r="BD31" s="5"/>
       <c r="BE31" s="5"/>
       <c r="BF31" s="5"/>
       <c r="BG31" s="5"/>
-    </row>
-    <row r="32" spans="1:59">
-      <c r="A32" s="7" t="s">
+      <c r="BH31" s="5"/>
+      <c r="BI31" s="5"/>
+    </row>
+    <row r="32" spans="1:61">
+      <c r="A32" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -3969,13 +4071,13 @@
         <v>21.72</v>
       </c>
       <c r="H32" s="5">
-        <v>20.55</v>
+        <v>20.43</v>
       </c>
       <c r="I32" s="5">
         <v>20.66</v>
       </c>
       <c r="J32" s="5">
-        <v>20.55</v>
+        <v>20.49</v>
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
@@ -4036,17 +4138,19 @@
       <c r="AW32" s="5"/>
       <c r="AX32" s="5"/>
       <c r="AY32" s="5"/>
-      <c r="AZ32" s="5"/>
+      <c r="AZ32" s="7"/>
       <c r="BA32" s="5"/>
-      <c r="BB32" s="5"/>
+      <c r="BB32" s="7"/>
       <c r="BC32" s="5"/>
       <c r="BD32" s="5"/>
       <c r="BE32" s="5"/>
       <c r="BF32" s="5"/>
       <c r="BG32" s="5"/>
-    </row>
-    <row r="33" spans="1:59">
-      <c r="A33" s="8" t="s">
+      <c r="BH32" s="5"/>
+      <c r="BI32" s="5"/>
+    </row>
+    <row r="33" spans="1:61">
+      <c r="A33" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -4133,17 +4237,19 @@
       <c r="AW33" s="5"/>
       <c r="AX33" s="5"/>
       <c r="AY33" s="5"/>
-      <c r="AZ33" s="5"/>
+      <c r="AZ33" s="7"/>
       <c r="BA33" s="5"/>
-      <c r="BB33" s="5"/>
+      <c r="BB33" s="7"/>
       <c r="BC33" s="5"/>
       <c r="BD33" s="5"/>
       <c r="BE33" s="5"/>
       <c r="BF33" s="5"/>
       <c r="BG33" s="5"/>
-    </row>
-    <row r="34" spans="1:59">
-      <c r="A34" s="7" t="s">
+      <c r="BH33" s="5"/>
+      <c r="BI33" s="5"/>
+    </row>
+    <row r="34" spans="1:61">
+      <c r="A34" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -4236,21 +4342,25 @@
         <v>17.850000000000001</v>
       </c>
       <c r="AW34" s="5">
-        <v>17.850000000000001</v>
+        <v>17.829999999999998</v>
       </c>
       <c r="AX34" s="5"/>
       <c r="AY34" s="5"/>
-      <c r="AZ34" s="5"/>
+      <c r="AZ34" s="7"/>
       <c r="BA34" s="5"/>
-      <c r="BB34" s="5"/>
+      <c r="BB34" s="7">
+        <v>17.72</v>
+      </c>
       <c r="BC34" s="5"/>
       <c r="BD34" s="5"/>
       <c r="BE34" s="5"/>
       <c r="BF34" s="5"/>
       <c r="BG34" s="5"/>
-    </row>
-    <row r="35" spans="1:59">
-      <c r="A35" s="8" t="s">
+      <c r="BH34" s="5"/>
+      <c r="BI34" s="5"/>
+    </row>
+    <row r="35" spans="1:61">
+      <c r="A35" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -4325,17 +4435,19 @@
       <c r="AW35" s="5"/>
       <c r="AX35" s="5"/>
       <c r="AY35" s="5"/>
-      <c r="AZ35" s="5"/>
+      <c r="AZ35" s="7"/>
       <c r="BA35" s="5"/>
-      <c r="BB35" s="5"/>
+      <c r="BB35" s="7"/>
       <c r="BC35" s="5"/>
       <c r="BD35" s="5"/>
       <c r="BE35" s="5"/>
       <c r="BF35" s="5"/>
       <c r="BG35" s="5"/>
-    </row>
-    <row r="36" spans="1:59">
-      <c r="A36" s="7" t="s">
+      <c r="BH35" s="5"/>
+      <c r="BI35" s="5"/>
+    </row>
+    <row r="36" spans="1:61">
+      <c r="A36" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -4424,17 +4536,19 @@
       <c r="AW36" s="5"/>
       <c r="AX36" s="5"/>
       <c r="AY36" s="5"/>
-      <c r="AZ36" s="5"/>
+      <c r="AZ36" s="7"/>
       <c r="BA36" s="5"/>
-      <c r="BB36" s="5"/>
+      <c r="BB36" s="7"/>
       <c r="BC36" s="5"/>
       <c r="BD36" s="5"/>
       <c r="BE36" s="5"/>
       <c r="BF36" s="5"/>
       <c r="BG36" s="5"/>
-    </row>
-    <row r="37" spans="1:59">
-      <c r="A37" s="8" t="s">
+      <c r="BH36" s="5"/>
+      <c r="BI36" s="5"/>
+    </row>
+    <row r="37" spans="1:61">
+      <c r="A37" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -4523,17 +4637,19 @@
       <c r="AW37" s="5"/>
       <c r="AX37" s="5"/>
       <c r="AY37" s="5"/>
-      <c r="AZ37" s="5"/>
+      <c r="AZ37" s="7"/>
       <c r="BA37" s="5"/>
-      <c r="BB37" s="5"/>
+      <c r="BB37" s="7"/>
       <c r="BC37" s="5"/>
       <c r="BD37" s="5"/>
       <c r="BE37" s="5"/>
       <c r="BF37" s="5"/>
       <c r="BG37" s="5"/>
-    </row>
-    <row r="38" spans="1:59">
-      <c r="A38" s="7" t="s">
+      <c r="BH37" s="5"/>
+      <c r="BI37" s="5"/>
+    </row>
+    <row r="38" spans="1:61">
+      <c r="A38" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -4598,17 +4714,19 @@
       <c r="AW38" s="5"/>
       <c r="AX38" s="5"/>
       <c r="AY38" s="5"/>
-      <c r="AZ38" s="5"/>
+      <c r="AZ38" s="7"/>
       <c r="BA38" s="5"/>
-      <c r="BB38" s="5"/>
+      <c r="BB38" s="7"/>
       <c r="BC38" s="5"/>
       <c r="BD38" s="5"/>
       <c r="BE38" s="5"/>
       <c r="BF38" s="5"/>
       <c r="BG38" s="5"/>
-    </row>
-    <row r="39" spans="1:59">
-      <c r="A39" s="8" t="s">
+      <c r="BH38" s="5"/>
+      <c r="BI38" s="5"/>
+    </row>
+    <row r="39" spans="1:61">
+      <c r="A39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -4675,24 +4793,26 @@
       <c r="AW39" s="5"/>
       <c r="AX39" s="5"/>
       <c r="AY39" s="5"/>
-      <c r="AZ39" s="5"/>
+      <c r="AZ39" s="7"/>
       <c r="BA39" s="5"/>
-      <c r="BB39" s="5"/>
+      <c r="BB39" s="7"/>
       <c r="BC39" s="5"/>
       <c r="BD39" s="5"/>
       <c r="BE39" s="5"/>
       <c r="BF39" s="5"/>
       <c r="BG39" s="5"/>
-    </row>
-    <row r="40" spans="1:59">
-      <c r="A40" s="7" t="s">
+      <c r="BH39" s="5"/>
+      <c r="BI39" s="5"/>
+    </row>
+    <row r="40" spans="1:61">
+      <c r="A40" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C40" s="5">
-        <v>27.13</v>
+        <v>27.07</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -4729,7 +4849,9 @@
       <c r="X40" s="5"/>
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
-      <c r="AA40" s="5"/>
+      <c r="AA40" s="5">
+        <v>29.33</v>
+      </c>
       <c r="AB40" s="5"/>
       <c r="AC40" s="5"/>
       <c r="AD40" s="5"/>
@@ -4754,26 +4876,32 @@
       <c r="AW40" s="5"/>
       <c r="AX40" s="5"/>
       <c r="AY40" s="5"/>
-      <c r="AZ40" s="5"/>
+      <c r="AZ40" s="7"/>
       <c r="BA40" s="5"/>
-      <c r="BB40" s="5"/>
+      <c r="BB40" s="7"/>
       <c r="BC40" s="5"/>
       <c r="BD40" s="5"/>
       <c r="BE40" s="5"/>
       <c r="BF40" s="5"/>
       <c r="BG40" s="5"/>
-    </row>
-    <row r="41" spans="1:59">
-      <c r="A41" s="8" t="s">
+      <c r="BH40" s="5"/>
+      <c r="BI40" s="5"/>
+    </row>
+    <row r="41" spans="1:61">
+      <c r="A41" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="5"/>
+      <c r="C41" s="5">
+        <v>21.96</v>
+      </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
+      <c r="F41" s="5">
+        <v>22.69</v>
+      </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5">
@@ -4801,16 +4929,22 @@
       <c r="U41" s="5"/>
       <c r="V41" s="5"/>
       <c r="W41" s="5"/>
-      <c r="X41" s="5"/>
+      <c r="X41" s="5">
+        <v>22.26</v>
+      </c>
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
-      <c r="AA41" s="5"/>
+      <c r="AA41" s="5">
+        <v>22.89</v>
+      </c>
       <c r="AB41" s="5"/>
       <c r="AC41" s="5"/>
       <c r="AD41" s="5"/>
       <c r="AE41" s="5"/>
       <c r="AF41" s="5"/>
-      <c r="AG41" s="5"/>
+      <c r="AG41" s="5">
+        <v>22.49</v>
+      </c>
       <c r="AH41" s="5"/>
       <c r="AI41" s="5"/>
       <c r="AJ41" s="5"/>
@@ -4826,34 +4960,44 @@
       <c r="AT41" s="5"/>
       <c r="AU41" s="5"/>
       <c r="AV41" s="5"/>
-      <c r="AW41" s="5"/>
+      <c r="AW41" s="5">
+        <v>23.09</v>
+      </c>
       <c r="AX41" s="5"/>
       <c r="AY41" s="5"/>
-      <c r="AZ41" s="5"/>
-      <c r="BA41" s="5"/>
-      <c r="BB41" s="5"/>
+      <c r="AZ41" s="7"/>
+      <c r="BA41" s="5">
+        <v>23.16</v>
+      </c>
+      <c r="BB41" s="7"/>
       <c r="BC41" s="5"/>
       <c r="BD41" s="5"/>
       <c r="BE41" s="5"/>
       <c r="BF41" s="5"/>
       <c r="BG41" s="5"/>
-    </row>
-    <row r="42" spans="1:59">
-      <c r="A42" s="7" t="s">
+      <c r="BH41" s="5"/>
+      <c r="BI41" s="5"/>
+    </row>
+    <row r="42" spans="1:61">
+      <c r="A42" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C42" s="5">
-        <v>26</v>
+        <v>24.3</v>
       </c>
       <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
+      <c r="E42" s="5">
+        <v>25.46</v>
+      </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
+      <c r="I42" s="5">
+        <v>25.56</v>
+      </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5">
         <v>25.44</v>
@@ -4869,7 +5013,9 @@
       <c r="P42" s="5">
         <v>25.59</v>
       </c>
-      <c r="Q42" s="5"/>
+      <c r="Q42" s="5">
+        <v>25.73</v>
+      </c>
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
@@ -4879,11 +5025,15 @@
       <c r="X42" s="5"/>
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
-      <c r="AA42" s="5"/>
+      <c r="AA42" s="5">
+        <v>25.7</v>
+      </c>
       <c r="AB42" s="5"/>
       <c r="AC42" s="5"/>
       <c r="AD42" s="5"/>
-      <c r="AE42" s="5"/>
+      <c r="AE42" s="5">
+        <v>25.56</v>
+      </c>
       <c r="AF42" s="5"/>
       <c r="AG42" s="5"/>
       <c r="AH42" s="5"/>
@@ -4904,17 +5054,19 @@
       <c r="AW42" s="5"/>
       <c r="AX42" s="5"/>
       <c r="AY42" s="5"/>
-      <c r="AZ42" s="5"/>
+      <c r="AZ42" s="7"/>
       <c r="BA42" s="5"/>
-      <c r="BB42" s="5"/>
+      <c r="BB42" s="7"/>
       <c r="BC42" s="5"/>
       <c r="BD42" s="5"/>
       <c r="BE42" s="5"/>
       <c r="BF42" s="5"/>
       <c r="BG42" s="5"/>
-    </row>
-    <row r="43" spans="1:59">
-      <c r="A43" s="8" t="s">
+      <c r="BH42" s="5"/>
+      <c r="BI42" s="5"/>
+    </row>
+    <row r="43" spans="1:61">
+      <c r="A43" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -4924,12 +5076,18 @@
         <v>25.3</v>
       </c>
       <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
+      <c r="E43" s="5">
+        <v>25.92</v>
+      </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
+      <c r="H43" s="5">
+        <v>25.18</v>
+      </c>
       <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
+      <c r="J43" s="5">
+        <v>26.48</v>
+      </c>
       <c r="K43" s="5">
         <v>25.74</v>
       </c>
@@ -4944,7 +5102,9 @@
       <c r="P43" s="5">
         <v>25.62</v>
       </c>
-      <c r="Q43" s="5"/>
+      <c r="Q43" s="5">
+        <v>26.23</v>
+      </c>
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
@@ -4954,7 +5114,9 @@
       <c r="X43" s="5"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
-      <c r="AA43" s="5"/>
+      <c r="AA43" s="5">
+        <v>26.49</v>
+      </c>
       <c r="AB43" s="5"/>
       <c r="AC43" s="5"/>
       <c r="AD43" s="5"/>
@@ -4979,30 +5141,42 @@
       <c r="AW43" s="5"/>
       <c r="AX43" s="5"/>
       <c r="AY43" s="5"/>
-      <c r="AZ43" s="5"/>
+      <c r="AZ43" s="7"/>
       <c r="BA43" s="5"/>
-      <c r="BB43" s="5"/>
+      <c r="BB43" s="7"/>
       <c r="BC43" s="5"/>
       <c r="BD43" s="5"/>
       <c r="BE43" s="5"/>
       <c r="BF43" s="5"/>
       <c r="BG43" s="5"/>
-    </row>
-    <row r="44" spans="1:59">
-      <c r="A44" s="7" t="s">
+      <c r="BH43" s="5"/>
+      <c r="BI43" s="5"/>
+    </row>
+    <row r="44" spans="1:61">
+      <c r="A44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="5"/>
+      <c r="C44" s="5">
+        <v>23.13</v>
+      </c>
       <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
+      <c r="E44" s="5">
+        <v>23.79</v>
+      </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
+      <c r="H44" s="5">
+        <v>23.7</v>
+      </c>
+      <c r="I44" s="5">
+        <v>24.29</v>
+      </c>
+      <c r="J44" s="5">
+        <v>23.49</v>
+      </c>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
@@ -5019,14 +5193,18 @@
       <c r="X44" s="5"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
-      <c r="AA44" s="5"/>
+      <c r="AA44" s="5">
+        <v>24.69</v>
+      </c>
       <c r="AB44" s="5"/>
       <c r="AC44" s="5"/>
       <c r="AD44" s="5"/>
       <c r="AE44" s="5"/>
       <c r="AF44" s="5"/>
       <c r="AG44" s="5"/>
-      <c r="AH44" s="5"/>
+      <c r="AH44" s="5">
+        <v>24.66</v>
+      </c>
       <c r="AI44" s="5"/>
       <c r="AJ44" s="5"/>
       <c r="AK44" s="5"/>
@@ -5044,37 +5222,55 @@
       <c r="AW44" s="5"/>
       <c r="AX44" s="5"/>
       <c r="AY44" s="5"/>
-      <c r="AZ44" s="5"/>
+      <c r="AZ44" s="7">
+        <v>24.89</v>
+      </c>
       <c r="BA44" s="5"/>
-      <c r="BB44" s="5"/>
+      <c r="BB44" s="7">
+        <v>24.9</v>
+      </c>
       <c r="BC44" s="5"/>
       <c r="BD44" s="5"/>
       <c r="BE44" s="5"/>
       <c r="BF44" s="5"/>
       <c r="BG44" s="5"/>
-    </row>
-    <row r="45" spans="1:59">
-      <c r="A45" s="8" t="s">
+      <c r="BH44" s="5"/>
+      <c r="BI44" s="5"/>
+    </row>
+    <row r="45" spans="1:61">
+      <c r="A45" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C45" s="5"/>
+      <c r="C45" s="5">
+        <v>23.39</v>
+      </c>
       <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
+      <c r="E45" s="5">
+        <v>24.56</v>
+      </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
+      <c r="H45" s="5">
+        <v>24.06</v>
+      </c>
+      <c r="I45" s="5">
+        <v>24.89</v>
+      </c>
+      <c r="J45" s="5">
+        <v>24.09</v>
+      </c>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
       <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
+      <c r="Q45" s="5">
+        <v>24.99</v>
+      </c>
       <c r="R45" s="5"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5"/>
@@ -5084,7 +5280,9 @@
       <c r="X45" s="5"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
-      <c r="AA45" s="5"/>
+      <c r="AA45" s="5">
+        <v>24.79</v>
+      </c>
       <c r="AB45" s="5"/>
       <c r="AC45" s="5"/>
       <c r="AD45" s="5"/>
@@ -5109,17 +5307,21 @@
       <c r="AW45" s="5"/>
       <c r="AX45" s="5"/>
       <c r="AY45" s="5"/>
-      <c r="AZ45" s="5"/>
+      <c r="AZ45" s="7">
+        <v>25.09</v>
+      </c>
       <c r="BA45" s="5"/>
-      <c r="BB45" s="5"/>
+      <c r="BB45" s="7"/>
       <c r="BC45" s="5"/>
       <c r="BD45" s="5"/>
       <c r="BE45" s="5"/>
       <c r="BF45" s="5"/>
       <c r="BG45" s="5"/>
+      <c r="BH45" s="5"/>
+      <c r="BI45" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:BI45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="22">
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
@@ -7519,13 +7721,12 @@
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultColWidth="7.453125" defaultRowHeight="14"/>
   <cols>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="1" max="2" width="14" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="3" max="3" width="11.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="4" max="4" width="9.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="5" max="5" width="9.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="6" max="6" width="10.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="7" max="7" width="13.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="8" max="8" width="14.0" customWidth="1"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -7555,7 +7756,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -7569,7 +7770,7 @@
       <c r="H2" s="5"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -7583,7 +7784,7 @@
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -7597,7 +7798,7 @@
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -7613,7 +7814,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -7627,7 +7828,7 @@
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -7641,7 +7842,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -7655,7 +7856,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -7669,7 +7870,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -7687,7 +7888,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -7701,7 +7902,7 @@
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -7715,7 +7916,7 @@
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -7731,7 +7932,7 @@
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -7745,7 +7946,7 @@
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -7759,7 +7960,7 @@
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -7773,7 +7974,7 @@
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -7787,7 +7988,7 @@
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -7801,7 +8002,7 @@
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -7817,7 +8018,7 @@
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -7831,7 +8032,7 @@
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -7845,7 +8046,7 @@
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -7859,7 +8060,7 @@
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -7873,7 +8074,7 @@
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -7887,7 +8088,7 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -7901,7 +8102,7 @@
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -7917,7 +8118,7 @@
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -7931,7 +8132,7 @@
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -7947,7 +8148,7 @@
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -7961,7 +8162,7 @@
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -7975,7 +8176,7 @@
       <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -7989,7 +8190,7 @@
       <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -8003,7 +8204,7 @@
       <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -8019,7 +8220,7 @@
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -8035,7 +8236,7 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -8049,7 +8250,7 @@
       <c r="H35" s="5"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -8063,7 +8264,7 @@
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -8077,7 +8278,7 @@
       <c r="H37" s="5"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -8091,7 +8292,7 @@
       <c r="H38" s="5"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -8105,7 +8306,7 @@
       <c r="H39" s="5"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -8119,7 +8320,7 @@
       <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -8133,7 +8334,7 @@
       <c r="H41" s="5"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -8147,7 +8348,7 @@
       <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -8161,7 +8362,7 @@
       <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -8175,7 +8376,7 @@
       <c r="H44" s="5"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -8224,13 +8425,12 @@
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultColWidth="7.453125" defaultRowHeight="14"/>
   <cols>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="1" max="2" width="14" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="3" max="3" width="11.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="4" max="4" width="9.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="5" max="5" width="9.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="6" max="6" width="10.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="7" max="7" width="13.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="8" max="8" width="14.0" customWidth="1"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8260,7 +8460,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -8274,7 +8474,7 @@
       <c r="H2" s="5"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -8288,7 +8488,7 @@
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -8302,7 +8502,7 @@
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -8318,7 +8518,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -8332,7 +8532,7 @@
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -8346,7 +8546,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -8360,7 +8560,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -8374,7 +8574,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -8392,7 +8592,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -8406,7 +8606,7 @@
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -8420,7 +8620,7 @@
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -8436,7 +8636,7 @@
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -8450,7 +8650,7 @@
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -8464,7 +8664,7 @@
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -8478,7 +8678,7 @@
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -8492,7 +8692,7 @@
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -8506,7 +8706,7 @@
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -8522,7 +8722,7 @@
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -8536,7 +8736,7 @@
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -8550,7 +8750,7 @@
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -8564,7 +8764,7 @@
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -8578,7 +8778,7 @@
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -8592,7 +8792,7 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -8606,7 +8806,7 @@
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -8622,7 +8822,7 @@
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -8636,7 +8836,7 @@
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -8652,7 +8852,7 @@
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -8666,7 +8866,7 @@
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -8680,7 +8880,7 @@
       <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -8694,7 +8894,7 @@
       <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -8708,7 +8908,7 @@
       <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -8724,7 +8924,7 @@
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -8740,7 +8940,7 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -8754,7 +8954,7 @@
       <c r="H35" s="5"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -8768,7 +8968,7 @@
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -8782,7 +8982,7 @@
       <c r="H37" s="5"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -8796,7 +8996,7 @@
       <c r="H38" s="5"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -8810,7 +9010,7 @@
       <c r="H39" s="5"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -8824,7 +9024,7 @@
       <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -8838,7 +9038,7 @@
       <c r="H41" s="5"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -8852,7 +9052,7 @@
       <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -8866,7 +9066,7 @@
       <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -8880,7 +9080,7 @@
       <c r="H44" s="5"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -8941,7 +9141,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -8949,7 +9149,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -8957,7 +9157,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -8965,7 +9165,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -8973,7 +9173,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -8981,7 +9181,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -8989,7 +9189,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -8997,7 +9197,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -9005,7 +9205,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -9013,7 +9213,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -9021,7 +9221,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -9029,7 +9229,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -9037,7 +9237,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -9045,7 +9245,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -9053,7 +9253,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -9061,7 +9261,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -9069,7 +9269,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -9077,7 +9277,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -9085,7 +9285,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -9093,7 +9293,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -9101,7 +9301,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -9109,7 +9309,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -9117,7 +9317,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -9125,7 +9325,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -9133,7 +9333,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -9141,7 +9341,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -9149,7 +9349,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -9157,7 +9357,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -9165,7 +9365,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -9173,7 +9373,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -9181,7 +9381,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -9189,7 +9389,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -9197,7 +9397,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -9205,7 +9405,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -9213,7 +9413,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -9221,7 +9421,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -9229,7 +9429,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -9237,7 +9437,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -9245,7 +9445,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -9253,7 +9453,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -9261,7 +9461,7 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -9269,7 +9469,7 @@
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -9277,7 +9477,7 @@
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -9285,7 +9485,7 @@
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -9328,14 +9528,11 @@
   <dimension ref="A1:I45"/>
   <sheetFormatPr defaultColWidth="7.453125" defaultRowHeight="14"/>
   <cols>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="1" max="2" width="14" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="3" max="3" width="11.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="4" max="4" width="7.453125" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="5" max="5" width="10.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="6" max="6" width="7.453125" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="7" max="7" width="7.453125" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="8" max="8" width="7.453125" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="9" max="9" width="7.453125" customWidth="1"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="7.453125" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="9" width="7.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -9368,7 +9565,7 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -9383,7 +9580,7 @@
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -9398,7 +9595,7 @@
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -9413,7 +9610,7 @@
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -9428,7 +9625,7 @@
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -9443,7 +9640,7 @@
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -9458,7 +9655,7 @@
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -9473,7 +9670,7 @@
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -9488,7 +9685,7 @@
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -9503,7 +9700,7 @@
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -9520,7 +9717,7 @@
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -9535,7 +9732,7 @@
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -9552,7 +9749,7 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -9567,7 +9764,7 @@
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -9582,7 +9779,7 @@
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -9597,7 +9794,7 @@
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -9612,7 +9809,7 @@
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -9627,7 +9824,7 @@
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -9642,7 +9839,7 @@
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -9657,7 +9854,7 @@
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -9674,7 +9871,7 @@
       <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -9689,7 +9886,7 @@
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -9704,7 +9901,7 @@
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -9719,7 +9916,7 @@
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -9734,7 +9931,7 @@
       <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -9749,7 +9946,7 @@
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -9764,7 +9961,7 @@
       <c r="I27" s="5"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -9779,7 +9976,7 @@
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -9794,7 +9991,7 @@
       <c r="I29" s="5"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -9809,7 +10006,7 @@
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -9824,7 +10021,7 @@
       <c r="I31" s="5"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -9839,7 +10036,7 @@
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -9854,7 +10051,7 @@
       <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -9869,7 +10066,7 @@
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -9884,7 +10081,7 @@
       <c r="I35" s="5"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -9899,7 +10096,7 @@
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -9914,7 +10111,7 @@
       <c r="I37" s="5"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -9929,7 +10126,7 @@
       <c r="I38" s="5"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -9944,7 +10141,7 @@
       <c r="I39" s="5"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -9959,7 +10156,7 @@
       <c r="I40" s="5"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -9974,7 +10171,7 @@
       <c r="I41" s="5"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -9989,7 +10186,7 @@
       <c r="I42" s="5"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -10004,7 +10201,7 @@
       <c r="I43" s="5"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -10019,7 +10216,7 @@
       <c r="I44" s="5"/>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -10069,13 +10266,12 @@
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultColWidth="7.453125" defaultRowHeight="14"/>
   <cols>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="1" max="2" width="14" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="3" max="3" width="11.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="4" max="4" width="9.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="5" max="5" width="9.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="6" max="6" width="10.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="7" max="7" width="13.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="8" max="8" width="14.0" customWidth="1"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -10105,7 +10301,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -10119,7 +10315,7 @@
       <c r="H2" s="5"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -10133,7 +10329,7 @@
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -10147,7 +10343,7 @@
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -10163,7 +10359,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -10177,7 +10373,7 @@
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -10191,7 +10387,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -10205,7 +10401,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -10219,7 +10415,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -10237,7 +10433,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -10251,7 +10447,7 @@
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -10265,7 +10461,7 @@
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -10281,7 +10477,7 @@
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -10295,7 +10491,7 @@
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -10309,7 +10505,7 @@
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -10323,7 +10519,7 @@
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -10337,7 +10533,7 @@
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -10351,7 +10547,7 @@
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -10367,7 +10563,7 @@
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -10381,7 +10577,7 @@
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -10395,7 +10591,7 @@
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -10409,7 +10605,7 @@
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -10423,7 +10619,7 @@
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -10437,7 +10633,7 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -10451,7 +10647,7 @@
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -10467,7 +10663,7 @@
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -10481,7 +10677,7 @@
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -10497,7 +10693,7 @@
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -10511,7 +10707,7 @@
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -10525,7 +10721,7 @@
       <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -10539,7 +10735,7 @@
       <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -10553,7 +10749,7 @@
       <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -10569,7 +10765,7 @@
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -10585,7 +10781,7 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -10599,7 +10795,7 @@
       <c r="H35" s="5"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -10613,7 +10809,7 @@
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -10627,7 +10823,7 @@
       <c r="H37" s="5"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -10641,7 +10837,7 @@
       <c r="H38" s="5"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -10655,7 +10851,7 @@
       <c r="H39" s="5"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -10669,7 +10865,7 @@
       <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -10683,7 +10879,7 @@
       <c r="H41" s="5"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -10697,7 +10893,7 @@
       <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -10711,7 +10907,7 @@
       <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -10725,7 +10921,7 @@
       <c r="H44" s="5"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -10774,13 +10970,12 @@
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultColWidth="7.453125" defaultRowHeight="14"/>
   <cols>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="1" max="2" width="14" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="3" max="3" width="11.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="4" max="4" width="9.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="5" max="5" width="9.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="6" max="6" width="10.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="7" max="7" width="13.0" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="8" max="8" width="14.0" customWidth="1"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -10810,7 +11005,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -10824,7 +11019,7 @@
       <c r="H2" s="5"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -10838,7 +11033,7 @@
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -10852,7 +11047,7 @@
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -10868,7 +11063,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -10882,7 +11077,7 @@
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -10896,7 +11091,7 @@
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -10910,7 +11105,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -10924,7 +11119,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -10942,7 +11137,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -10956,7 +11151,7 @@
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -10970,7 +11165,7 @@
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -10986,7 +11181,7 @@
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -11000,7 +11195,7 @@
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -11014,7 +11209,7 @@
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -11028,7 +11223,7 @@
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -11042,7 +11237,7 @@
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -11056,7 +11251,7 @@
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -11072,7 +11267,7 @@
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -11086,7 +11281,7 @@
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -11100,7 +11295,7 @@
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -11114,7 +11309,7 @@
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -11128,7 +11323,7 @@
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -11142,7 +11337,7 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -11156,7 +11351,7 @@
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -11172,7 +11367,7 @@
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -11186,7 +11381,7 @@
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -11202,7 +11397,7 @@
       <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -11216,7 +11411,7 @@
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -11230,7 +11425,7 @@
       <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -11244,7 +11439,7 @@
       <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -11258,7 +11453,7 @@
       <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -11274,7 +11469,7 @@
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -11290,7 +11485,7 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -11304,7 +11499,7 @@
       <c r="H35" s="5"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -11318,7 +11513,7 @@
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -11332,7 +11527,7 @@
       <c r="H37" s="5"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -11346,7 +11541,7 @@
       <c r="H38" s="5"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -11360,7 +11555,7 @@
       <c r="H39" s="5"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -11374,7 +11569,7 @@
       <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -11388,7 +11583,7 @@
       <c r="H41" s="5"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -11402,7 +11597,7 @@
       <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -11416,7 +11611,7 @@
       <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -11430,7 +11625,7 @@
       <c r="H44" s="5"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -11491,7 +11686,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -11499,7 +11694,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -11507,7 +11702,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -11515,7 +11710,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -11523,7 +11718,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -11531,7 +11726,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -11539,7 +11734,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -11547,7 +11742,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -11555,7 +11750,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -11563,7 +11758,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -11571,7 +11766,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -11579,7 +11774,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -11587,7 +11782,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -11595,7 +11790,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -11603,7 +11798,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -11611,7 +11806,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -11619,7 +11814,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -11627,7 +11822,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -11635,7 +11830,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -11643,7 +11838,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -11651,7 +11846,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -11659,7 +11854,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -11667,7 +11862,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -11675,7 +11870,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -11683,7 +11878,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="9" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -11691,7 +11886,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -11699,7 +11894,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -11707,7 +11902,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -11715,7 +11910,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="9" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -11723,7 +11918,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -11731,7 +11926,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -11739,7 +11934,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -11747,7 +11942,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -11755,7 +11950,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -11763,7 +11958,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -11771,7 +11966,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -11779,7 +11974,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -11787,7 +11982,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -11795,7 +11990,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -11803,7 +11998,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -11811,7 +12006,7 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -11819,7 +12014,7 @@
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -11827,7 +12022,7 @@
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -11835,7 +12030,7 @@
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -11875,7 +12070,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr defaultColWidth="7.453125" defaultRowHeight="14"/>
   <cols>
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="1" max="2" width="14" customWidth="1"/>
@@ -11899,10 +12094,11 @@
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="20" max="20" width="9.0" customWidth="1"/>
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="21" max="21" width="7.453125" customWidth="1"/>
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="22" max="22" width="7.453125" customWidth="1"/>
-    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="23" max="23" width="7.5" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="23" max="23" width="9.0" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="24" max="24" width="7.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -11969,11 +12165,14 @@
       <c r="V1" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="X1" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
@@ -12006,9 +12205,10 @@
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-    </row>
-    <row r="3" spans="1:23">
+      <c r="W2" s="7"/>
+      <c r="X2" s="5"/>
+    </row>
+    <row r="3" spans="1:24">
       <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
@@ -12051,9 +12251,12 @@
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
       <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-    </row>
-    <row r="4" spans="1:23">
+      <c r="W3" s="7">
+        <v>22.03</v>
+      </c>
+      <c r="X3" s="5"/>
+    </row>
+    <row r="4" spans="1:24">
       <c r="A4" s="6" t="s">
         <v>17</v>
       </c>
@@ -12110,9 +12313,10 @@
       <c r="V4" s="5">
         <v>21.7</v>
       </c>
-      <c r="W4" s="5"/>
-    </row>
-    <row r="5" spans="1:23">
+      <c r="W4" s="7"/>
+      <c r="X4" s="5"/>
+    </row>
+    <row r="5" spans="1:24">
       <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
@@ -12138,7 +12342,9 @@
       <c r="I5" s="5">
         <v>17.100000000000001</v>
       </c>
-      <c r="J5" s="5"/>
+      <c r="J5" s="5">
+        <v>17.670000000000002</v>
+      </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -12155,11 +12361,14 @@
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
-      <c r="W5" s="5">
+      <c r="W5" s="7">
+        <v>17.96</v>
+      </c>
+      <c r="X5" s="5">
         <v>18.399000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" s="6" t="s">
         <v>23</v>
       </c>
@@ -12198,9 +12407,10 @@
         <v>18.5</v>
       </c>
       <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-    </row>
-    <row r="7" spans="1:23">
+      <c r="W6" s="7"/>
+      <c r="X6" s="5"/>
+    </row>
+    <row r="7" spans="1:24">
       <c r="A7" s="6" t="s">
         <v>26</v>
       </c>
@@ -12231,9 +12441,10 @@
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-    </row>
-    <row r="8" spans="1:23">
+      <c r="W7" s="7"/>
+      <c r="X7" s="5"/>
+    </row>
+    <row r="8" spans="1:24">
       <c r="A8" s="6" t="s">
         <v>44</v>
       </c>
@@ -12264,9 +12475,10 @@
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-    </row>
-    <row r="9" spans="1:23">
+      <c r="W8" s="7"/>
+      <c r="X8" s="5"/>
+    </row>
+    <row r="9" spans="1:24">
       <c r="A9" s="6" t="s">
         <v>56</v>
       </c>
@@ -12305,9 +12517,10 @@
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-    </row>
-    <row r="10" spans="1:23">
+      <c r="W9" s="7"/>
+      <c r="X9" s="5"/>
+    </row>
+    <row r="10" spans="1:24">
       <c r="A10" s="6" t="s">
         <v>59</v>
       </c>
@@ -12340,10 +12553,11 @@
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W10" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <autoFilter ref="A1:X10" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/gauntlet_data.global.xlsx
+++ b/gauntlet_data.global.xlsx
@@ -893,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI45"/>
+  <dimension ref="A1:BJ45"/>
   <sheetFormatPr defaultColWidth="7.453125" defaultRowHeight="14"/>
   <cols>
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="1" max="1" width="14.36328125" bestFit="1" customWidth="1"/>
@@ -957,6 +957,7 @@
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="59" max="59" width="7.453125" customWidth="1"/>
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="60" max="60" width="9.0" customWidth="1"/>
     <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="61" max="61" width="10.0" customWidth="1"/>
+    <col xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" min="62" max="62" width="7.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:61">
@@ -1144,6 +1145,11 @@
       </c>
       <c r="BI1" s="3" t="s">
         <v>107</v>
+      </c>
+      <c r="BJ1" s="3" t="inlineStr">
+        <is>
+          <t>统治</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:61">
@@ -1240,6 +1246,7 @@
       <c r="BG2" s="5"/>
       <c r="BH2" s="5"/>
       <c r="BI2" s="5"/>
+      <c r="BJ2" s="5"/>
     </row>
     <row r="3" spans="1:61">
       <c r="A3" s="10" t="s">
@@ -1287,7 +1294,9 @@
       <c r="Q3" s="5">
         <v>17.13</v>
       </c>
-      <c r="R3" s="5"/>
+      <c r="R3" s="5">
+        <v>16.96</v>
+      </c>
       <c r="S3" s="5">
         <v>17.25</v>
       </c>
@@ -1357,6 +1366,7 @@
       <c r="BG3" s="5"/>
       <c r="BH3" s="5"/>
       <c r="BI3" s="5"/>
+      <c r="BJ3" s="5"/>
     </row>
     <row r="4" spans="1:61">
       <c r="A4" s="9" t="s">
@@ -1456,6 +1466,7 @@
       <c r="BG4" s="5"/>
       <c r="BH4" s="5"/>
       <c r="BI4" s="5"/>
+      <c r="BJ4" s="5"/>
     </row>
     <row r="5" spans="1:61">
       <c r="A5" s="10" t="s">
@@ -1524,7 +1535,9 @@
       <c r="AJ5" s="5"/>
       <c r="AK5" s="5"/>
       <c r="AL5" s="5"/>
-      <c r="AM5" s="5"/>
+      <c r="AM5" s="5">
+        <v>19.41</v>
+      </c>
       <c r="AN5" s="5"/>
       <c r="AO5" s="5"/>
       <c r="AP5" s="5"/>
@@ -1547,6 +1560,7 @@
       <c r="BG5" s="5"/>
       <c r="BH5" s="5"/>
       <c r="BI5" s="5"/>
+      <c r="BJ5" s="5"/>
     </row>
     <row r="6" spans="1:61">
       <c r="A6" s="9" t="s">
@@ -1642,6 +1656,7 @@
       <c r="BG6" s="5"/>
       <c r="BH6" s="5"/>
       <c r="BI6" s="5"/>
+      <c r="BJ6" s="5"/>
     </row>
     <row r="7" spans="1:61">
       <c r="A7" s="10" t="s">
@@ -1743,6 +1758,7 @@
       <c r="BG7" s="5"/>
       <c r="BH7" s="5"/>
       <c r="BI7" s="5"/>
+      <c r="BJ7" s="5"/>
     </row>
     <row r="8" spans="1:61">
       <c r="A8" s="9" t="s">
@@ -1793,7 +1809,7 @@
         <v>25.03</v>
       </c>
       <c r="R8" s="5">
-        <v>25.03</v>
+        <v>24.39</v>
       </c>
       <c r="S8" s="5">
         <v>24.65</v>
@@ -1846,13 +1862,16 @@
       <c r="BG8" s="5"/>
       <c r="BH8" s="5"/>
       <c r="BI8" s="5"/>
+      <c r="BJ8" s="5"/>
     </row>
     <row r="9" spans="1:61">
       <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>双重环道</t>
+        </is>
       </c>
       <c r="C9" s="5">
         <v>26.65</v>
@@ -1898,7 +1917,7 @@
         <v>27.99</v>
       </c>
       <c r="R9" s="5">
-        <v>27.76</v>
+        <v>27.09</v>
       </c>
       <c r="S9" s="5">
         <v>27.75</v>
@@ -1961,6 +1980,7 @@
       <c r="BG9" s="5"/>
       <c r="BH9" s="5"/>
       <c r="BI9" s="5"/>
+      <c r="BJ9" s="5"/>
     </row>
     <row r="10" spans="1:61">
       <c r="A10" s="9" t="s">
@@ -1995,7 +2015,7 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5">
-        <v>22.83</v>
+        <v>22.59</v>
       </c>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
@@ -2052,6 +2072,9 @@
       <c r="BG10" s="5"/>
       <c r="BH10" s="5"/>
       <c r="BI10" s="5"/>
+      <c r="BJ10" s="5">
+        <v>23.59</v>
+      </c>
     </row>
     <row r="11" spans="1:61">
       <c r="A11" s="10" t="s">
@@ -2161,6 +2184,7 @@
       <c r="BG11" s="5"/>
       <c r="BH11" s="5"/>
       <c r="BI11" s="5"/>
+      <c r="BJ11" s="5"/>
     </row>
     <row r="12" spans="1:61">
       <c r="A12" s="9" t="s">
@@ -2240,6 +2264,7 @@
       <c r="BG12" s="5"/>
       <c r="BH12" s="5"/>
       <c r="BI12" s="5"/>
+      <c r="BJ12" s="5"/>
     </row>
     <row r="13" spans="1:61">
       <c r="A13" s="10" t="s">
@@ -2275,7 +2300,9 @@
       <c r="Q13" s="5">
         <v>23.67</v>
       </c>
-      <c r="R13" s="5"/>
+      <c r="R13" s="5">
+        <v>22.69</v>
+      </c>
       <c r="S13" s="5"/>
       <c r="T13" s="5">
         <v>23.25</v>
@@ -2329,6 +2356,7 @@
       <c r="BG13" s="5"/>
       <c r="BH13" s="5"/>
       <c r="BI13" s="5"/>
+      <c r="BJ13" s="5"/>
     </row>
     <row r="14" spans="1:61">
       <c r="A14" s="9" t="s">
@@ -2410,6 +2438,7 @@
       <c r="BG14" s="5"/>
       <c r="BH14" s="5"/>
       <c r="BI14" s="5"/>
+      <c r="BJ14" s="5"/>
     </row>
     <row r="15" spans="1:61">
       <c r="A15" s="10" t="s">
@@ -2505,6 +2534,7 @@
       <c r="BG15" s="5"/>
       <c r="BH15" s="5"/>
       <c r="BI15" s="5"/>
+      <c r="BJ15" s="5"/>
     </row>
     <row r="16" spans="1:61">
       <c r="A16" s="9" t="s">
@@ -2548,9 +2578,7 @@
       <c r="Q16" s="5">
         <v>21.87</v>
       </c>
-      <c r="R16" s="5">
-        <v>22.63</v>
-      </c>
+      <c r="R16" s="5"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
       <c r="U16" s="5">
@@ -2585,7 +2613,9 @@
       </c>
       <c r="AK16" s="5"/>
       <c r="AL16" s="5"/>
-      <c r="AM16" s="5"/>
+      <c r="AM16" s="5">
+        <v>22.9</v>
+      </c>
       <c r="AN16" s="5"/>
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
@@ -2608,6 +2638,7 @@
       <c r="BG16" s="5"/>
       <c r="BH16" s="5"/>
       <c r="BI16" s="5"/>
+      <c r="BJ16" s="5"/>
     </row>
     <row r="17" spans="1:61">
       <c r="A17" s="10" t="s">
@@ -2693,6 +2724,7 @@
       <c r="BG17" s="5"/>
       <c r="BH17" s="5"/>
       <c r="BI17" s="5"/>
+      <c r="BJ17" s="5"/>
     </row>
     <row r="18" spans="1:61">
       <c r="A18" s="9" t="s">
@@ -2790,6 +2822,7 @@
       <c r="BG18" s="5"/>
       <c r="BH18" s="5"/>
       <c r="BI18" s="5"/>
+      <c r="BJ18" s="5"/>
     </row>
     <row r="19" spans="1:61">
       <c r="A19" s="10" t="s">
@@ -2835,9 +2868,7 @@
       <c r="Q19" s="5">
         <v>22.13</v>
       </c>
-      <c r="R19" s="5">
-        <v>22.59</v>
-      </c>
+      <c r="R19" s="5"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <v>22.95</v>
@@ -2895,6 +2926,7 @@
       <c r="BG19" s="5"/>
       <c r="BH19" s="5"/>
       <c r="BI19" s="5"/>
+      <c r="BJ19" s="5"/>
     </row>
     <row r="20" spans="1:61">
       <c r="A20" s="9" t="s">
@@ -2990,6 +3022,7 @@
       <c r="BG20" s="5"/>
       <c r="BH20" s="5"/>
       <c r="BI20" s="5"/>
+      <c r="BJ20" s="5"/>
     </row>
     <row r="21" spans="1:61">
       <c r="A21" s="10" t="s">
@@ -3027,7 +3060,9 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
+      <c r="R21" s="5">
+        <v>20.02</v>
+      </c>
       <c r="S21" s="5">
         <v>20.34</v>
       </c>
@@ -3091,6 +3126,7 @@
       <c r="BG21" s="5"/>
       <c r="BH21" s="5"/>
       <c r="BI21" s="5"/>
+      <c r="BJ21" s="5"/>
     </row>
     <row r="22" spans="1:61">
       <c r="A22" s="9" t="s">
@@ -3163,7 +3199,9 @@
         <v>21.69</v>
       </c>
       <c r="AL22" s="5"/>
-      <c r="AM22" s="5"/>
+      <c r="AM22" s="5">
+        <v>21.7</v>
+      </c>
       <c r="AN22" s="5"/>
       <c r="AO22" s="5"/>
       <c r="AP22" s="5"/>
@@ -3186,6 +3224,7 @@
       <c r="BG22" s="5"/>
       <c r="BH22" s="5"/>
       <c r="BI22" s="5"/>
+      <c r="BJ22" s="5"/>
     </row>
     <row r="23" spans="1:61">
       <c r="A23" s="10" t="s">
@@ -3204,7 +3243,7 @@
         <v>20.99</v>
       </c>
       <c r="F23" s="5">
-        <v>21.6</v>
+        <v>21.65</v>
       </c>
       <c r="G23" s="5">
         <v>22.25</v>
@@ -3275,6 +3314,7 @@
       <c r="BG23" s="5"/>
       <c r="BH23" s="5"/>
       <c r="BI23" s="5"/>
+      <c r="BJ23" s="5"/>
     </row>
     <row r="24" spans="1:61">
       <c r="A24" s="9" t="s">
@@ -3325,7 +3365,7 @@
       </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="5">
-        <v>31.66</v>
+        <v>30.83</v>
       </c>
       <c r="S24" s="5">
         <v>31.25</v>
@@ -3376,6 +3416,7 @@
       <c r="BG24" s="5"/>
       <c r="BH24" s="5"/>
       <c r="BI24" s="5"/>
+      <c r="BJ24" s="5"/>
     </row>
     <row r="25" spans="1:61">
       <c r="A25" s="10" t="s">
@@ -3426,7 +3467,7 @@
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="5">
-        <v>24.19</v>
+        <v>23.69</v>
       </c>
       <c r="S25" s="5">
         <v>23.85</v>
@@ -3481,6 +3522,7 @@
       <c r="BG25" s="5"/>
       <c r="BH25" s="5"/>
       <c r="BI25" s="5"/>
+      <c r="BJ25" s="5"/>
     </row>
     <row r="26" spans="1:61">
       <c r="A26" s="9" t="s">
@@ -3582,6 +3624,7 @@
       <c r="BG26" s="5"/>
       <c r="BH26" s="5"/>
       <c r="BI26" s="5"/>
+      <c r="BJ26" s="5"/>
     </row>
     <row r="27" spans="1:61">
       <c r="A27" s="10" t="s">
@@ -3623,9 +3666,7 @@
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
-      <c r="R27" s="5">
-        <v>23.06</v>
-      </c>
+      <c r="R27" s="5"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
         <v>23.05</v>
@@ -3652,7 +3693,9 @@
         <v>23.19</v>
       </c>
       <c r="AL27" s="5"/>
-      <c r="AM27" s="5"/>
+      <c r="AM27" s="5">
+        <v>23.2</v>
+      </c>
       <c r="AN27" s="5"/>
       <c r="AO27" s="5"/>
       <c r="AP27" s="5"/>
@@ -3675,6 +3718,7 @@
       <c r="BG27" s="5"/>
       <c r="BH27" s="5"/>
       <c r="BI27" s="5"/>
+      <c r="BJ27" s="5"/>
     </row>
     <row r="28" spans="1:61">
       <c r="A28" s="9" t="s">
@@ -3717,7 +3761,7 @@
       </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="5">
-        <v>32.56</v>
+        <v>31.73</v>
       </c>
       <c r="S28" s="5"/>
       <c r="T28" s="5"/>
@@ -3764,6 +3808,7 @@
       <c r="BG28" s="5"/>
       <c r="BH28" s="5"/>
       <c r="BI28" s="5"/>
+      <c r="BJ28" s="5"/>
     </row>
     <row r="29" spans="1:61">
       <c r="A29" s="10" t="s">
@@ -3803,9 +3848,7 @@
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
-      <c r="R29" s="5">
-        <v>32.659999999999997</v>
-      </c>
+      <c r="R29" s="5"/>
       <c r="S29" s="5">
         <v>31.55</v>
       </c>
@@ -3863,6 +3906,7 @@
       <c r="BG29" s="5"/>
       <c r="BH29" s="5"/>
       <c r="BI29" s="5"/>
+      <c r="BJ29" s="5"/>
     </row>
     <row r="30" spans="1:61">
       <c r="A30" s="9" t="s">
@@ -3942,6 +3986,7 @@
       <c r="BG30" s="5"/>
       <c r="BH30" s="5"/>
       <c r="BI30" s="5"/>
+      <c r="BJ30" s="5"/>
     </row>
     <row r="31" spans="1:61">
       <c r="A31" s="10" t="s">
@@ -3989,9 +4034,7 @@
       <c r="Q31" s="5">
         <v>20.329999999999998</v>
       </c>
-      <c r="R31" s="5">
-        <v>20.46</v>
-      </c>
+      <c r="R31" s="5"/>
       <c r="S31" s="5">
         <v>20.55</v>
       </c>
@@ -4047,6 +4090,7 @@
       <c r="BG31" s="5"/>
       <c r="BH31" s="5"/>
       <c r="BI31" s="5"/>
+      <c r="BJ31" s="5"/>
     </row>
     <row r="32" spans="1:61">
       <c r="A32" s="9" t="s">
@@ -4089,7 +4133,7 @@
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
       <c r="R32" s="5">
-        <v>21.03</v>
+        <v>20.66</v>
       </c>
       <c r="S32" s="5"/>
       <c r="T32" s="5">
@@ -4148,6 +4192,7 @@
       <c r="BG32" s="5"/>
       <c r="BH32" s="5"/>
       <c r="BI32" s="5"/>
+      <c r="BJ32" s="5"/>
     </row>
     <row r="33" spans="1:61">
       <c r="A33" s="10" t="s">
@@ -4196,7 +4241,7 @@
       </c>
       <c r="Q33" s="5"/>
       <c r="R33" s="5">
-        <v>23.36</v>
+        <v>22.89</v>
       </c>
       <c r="S33" s="5">
         <v>22.95</v>
@@ -4247,6 +4292,7 @@
       <c r="BG33" s="5"/>
       <c r="BH33" s="5"/>
       <c r="BI33" s="5"/>
+      <c r="BJ33" s="5"/>
     </row>
     <row r="34" spans="1:61">
       <c r="A34" s="9" t="s">
@@ -4282,9 +4328,7 @@
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
-      <c r="R34" s="5">
-        <v>18.03</v>
-      </c>
+      <c r="R34" s="5"/>
       <c r="S34" s="5"/>
       <c r="T34" s="5">
         <v>17.350000000000001</v>
@@ -4358,6 +4402,7 @@
       <c r="BG34" s="5"/>
       <c r="BH34" s="5"/>
       <c r="BI34" s="5"/>
+      <c r="BJ34" s="5"/>
     </row>
     <row r="35" spans="1:61">
       <c r="A35" s="10" t="s">
@@ -4394,7 +4439,7 @@
       </c>
       <c r="Q35" s="5"/>
       <c r="R35" s="5">
-        <v>26.16</v>
+        <v>25.59</v>
       </c>
       <c r="S35" s="5"/>
       <c r="T35" s="5"/>
@@ -4445,6 +4490,7 @@
       <c r="BG35" s="5"/>
       <c r="BH35" s="5"/>
       <c r="BI35" s="5"/>
+      <c r="BJ35" s="5"/>
     </row>
     <row r="36" spans="1:61">
       <c r="A36" s="9" t="s">
@@ -4486,9 +4532,7 @@
       <c r="Q36" s="5">
         <v>20.53</v>
       </c>
-      <c r="R36" s="5">
-        <v>20.79</v>
-      </c>
+      <c r="R36" s="5"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5">
         <v>20.55</v>
@@ -4546,6 +4590,7 @@
       <c r="BG36" s="5"/>
       <c r="BH36" s="5"/>
       <c r="BI36" s="5"/>
+      <c r="BJ36" s="5"/>
     </row>
     <row r="37" spans="1:61">
       <c r="A37" s="10" t="s">
@@ -4590,7 +4635,7 @@
         <v>24.73</v>
       </c>
       <c r="R37" s="5">
-        <v>24.46</v>
+        <v>23.99</v>
       </c>
       <c r="S37" s="5">
         <v>24.55</v>
@@ -4647,6 +4692,7 @@
       <c r="BG37" s="5"/>
       <c r="BH37" s="5"/>
       <c r="BI37" s="5"/>
+      <c r="BJ37" s="5"/>
     </row>
     <row r="38" spans="1:61">
       <c r="A38" s="9" t="s">
@@ -4724,6 +4770,7 @@
       <c r="BG38" s="5"/>
       <c r="BH38" s="5"/>
       <c r="BI38" s="5"/>
+      <c r="BJ38" s="5"/>
     </row>
     <row r="39" spans="1:61">
       <c r="A39" s="10" t="s">
@@ -4803,6 +4850,7 @@
       <c r="BG39" s="5"/>
       <c r="BH39" s="5"/>
       <c r="BI39" s="5"/>
+      <c r="BJ39" s="5"/>
     </row>
     <row r="40" spans="1:61">
       <c r="A40" s="9" t="s">
@@ -4886,6 +4934,7 @@
       <c r="BG40" s="5"/>
       <c r="BH40" s="5"/>
       <c r="BI40" s="5"/>
+      <c r="BJ40" s="5"/>
     </row>
     <row r="41" spans="1:61">
       <c r="A41" s="10" t="s">
@@ -4923,7 +4972,9 @@
         <v>22.29</v>
       </c>
       <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
+      <c r="R41" s="5">
+        <v>21.96</v>
+      </c>
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
       <c r="U41" s="5"/>
@@ -4977,6 +5028,7 @@
       <c r="BG41" s="5"/>
       <c r="BH41" s="5"/>
       <c r="BI41" s="5"/>
+      <c r="BJ41" s="5"/>
     </row>
     <row r="42" spans="1:61">
       <c r="A42" s="9" t="s">
@@ -5016,7 +5068,9 @@
       <c r="Q42" s="5">
         <v>25.73</v>
       </c>
-      <c r="R42" s="5"/>
+      <c r="R42" s="5">
+        <v>25.09</v>
+      </c>
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
       <c r="U42" s="5"/>
@@ -5064,6 +5118,7 @@
       <c r="BG42" s="5"/>
       <c r="BH42" s="5"/>
       <c r="BI42" s="5"/>
+      <c r="BJ42" s="5"/>
     </row>
     <row r="43" spans="1:61">
       <c r="A43" s="10" t="s">
@@ -5151,6 +5206,7 @@
       <c r="BG43" s="5"/>
       <c r="BH43" s="5"/>
       <c r="BI43" s="5"/>
+      <c r="BJ43" s="5"/>
     </row>
     <row r="44" spans="1:61">
       <c r="A44" s="9" t="s">
@@ -5236,6 +5292,7 @@
       <c r="BG44" s="5"/>
       <c r="BH44" s="5"/>
       <c r="BI44" s="5"/>
+      <c r="BJ44" s="5"/>
     </row>
     <row r="45" spans="1:61">
       <c r="A45" s="10" t="s">
@@ -5319,9 +5376,10 @@
       <c r="BG45" s="5"/>
       <c r="BH45" s="5"/>
       <c r="BI45" s="5"/>
+      <c r="BJ45" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:BJ45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="22">
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
@@ -7859,8 +7917,10 @@
       <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>双重环道</t>
+        </is>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -8563,8 +8623,10 @@
       <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>双重环道</t>
+        </is>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -9200,8 +9262,10 @@
       <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>双重环道</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9673,8 +9737,10 @@
       <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>双重环道</t>
+        </is>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -10404,8 +10470,10 @@
       <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>双重环道</t>
+        </is>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -11108,8 +11176,10 @@
       <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>双重环道</t>
+        </is>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -11745,8 +11815,10 @@
       <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>双重环道</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:2">
